--- a/output/BOM_Intelligence_Report.xlsx
+++ b/output/BOM_Intelligence_Report.xlsx
@@ -21,8 +21,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Merge Candidate'!$A$1:$M$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Capacitor Summary'!$A$1:$I$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Merge Workspace'!$A$1:$K$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Resistor Summary'!$A$1:$I$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Merge Workspace'!$A$1:$L$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Resistor Summary'!$A$1:$H$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Resistor Detail'!$A$1:$I$125</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'AVL Candidate'!$A$1:$G$175</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Risk Review'!$A$1:$F$21</definedName>
@@ -773,7 +773,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Global health check: Dashboard shows scope; Summary queues review; RD records decisions in Merge Workspace.</t>
+          <t>Global health check: Dashboard shows scope; Summary queues review; RD records BOM Action in Merge Workspace.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-21T07:29:39+00:00  |  Rules: built-in defaults  |  Platform: 2.0.0</t>
+          <t>Generated: 2026-07-21T08:38:56+00:00  |  Rules: built-in defaults  |  Platform: 2.0.0</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>2026-07-21T07:29:39+00:00</t>
+          <t>2026-07-21T08:38:56+00:00</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr"/>
@@ -2613,7 +2613,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="H1" s="14" t="inlineStr">
         <is>
-          <t>RD Decision</t>
+          <t>BOM Action</t>
         </is>
       </c>
       <c r="I1" s="14" t="inlineStr">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H2" s="16">
-        <f>IFERROR(IF(VLOOKUP($A2,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A2,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A2,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A2,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I2" s="19" t="inlineStr">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="H3" s="15">
-        <f>IFERROR(IF(VLOOKUP($A3,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A3,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A3,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A3,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I3" s="19" t="inlineStr">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="H4" s="16">
-        <f>IFERROR(IF(VLOOKUP($A4,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A4,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A4,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A4,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I4" s="19" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="H5" s="15">
-        <f>IFERROR(IF(VLOOKUP($A5,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A5,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A5,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A5,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I5" s="19" t="inlineStr">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="H6" s="16">
-        <f>IFERROR(IF(VLOOKUP($A6,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A6,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A6,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A6,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I6" s="19" t="inlineStr">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="H7" s="15">
-        <f>IFERROR(IF(VLOOKUP($A7,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A7,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A7,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A7,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I7" s="19" t="inlineStr">
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="H8" s="16">
-        <f>IFERROR(IF(VLOOKUP($A8,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A8,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A8,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A8,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I8" s="19" t="inlineStr">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="H9" s="15">
-        <f>IFERROR(IF(VLOOKUP($A9,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A9,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A9,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A9,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I9" s="19" t="inlineStr">
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="H10" s="16">
-        <f>IFERROR(IF(VLOOKUP($A10,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A10,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A10,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A10,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I10" s="19" t="inlineStr">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="H11" s="15">
-        <f>IFERROR(IF(VLOOKUP($A11,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A11,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A11,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A11,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I11" s="19" t="inlineStr">
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="H12" s="16">
-        <f>IFERROR(IF(VLOOKUP($A12,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A12,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A12,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A12,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I12" s="19" t="inlineStr">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="H13" s="15">
-        <f>IFERROR(IF(VLOOKUP($A13,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A13,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A13,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A13,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I13" s="19" t="inlineStr">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="H14" s="16">
-        <f>IFERROR(IF(VLOOKUP($A14,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A14,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A14,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A14,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I14" s="19" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="H15" s="15">
-        <f>IFERROR(IF(VLOOKUP($A15,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A15,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A15,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A15,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I15" s="19" t="inlineStr">
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="H16" s="16">
-        <f>IFERROR(IF(VLOOKUP($A16,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A16,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A16,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A16,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I16" s="19" t="inlineStr">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="H17" s="15">
-        <f>IFERROR(IF(VLOOKUP($A17,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A17,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A17,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A17,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I17" s="19" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="H18" s="16">
-        <f>IFERROR(IF(VLOOKUP($A18,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A18,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A18,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A18,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I18" s="19" t="inlineStr">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="H19" s="15">
-        <f>IFERROR(IF(VLOOKUP($A19,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A19,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A19,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A19,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I19" s="19" t="inlineStr">
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="H20" s="16">
-        <f>IFERROR(IF(VLOOKUP($A20,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A20,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A20,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A20,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I20" s="19" t="inlineStr">
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="H21" s="15">
-        <f>IFERROR(IF(VLOOKUP($A21,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A21,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A21,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A21,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I21" s="19" t="inlineStr">
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="H22" s="16">
-        <f>IFERROR(IF(VLOOKUP($A22,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A22,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A22,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A22,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I22" s="19" t="inlineStr">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="H23" s="15">
-        <f>IFERROR(IF(VLOOKUP($A23,'Merge Workspace'!$A:$K,11,FALSE)="","Pending",VLOOKUP($A23,'Merge Workspace'!$A:$K,11,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A23,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A23,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I23" s="19" t="inlineStr">
@@ -3580,7 +3580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3588,12 +3588,13 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3624,32 +3625,37 @@
       </c>
       <c r="F1" s="14" t="inlineStr">
         <is>
+          <t>Affected RefDes</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>Estimated Modification</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="I1" s="14" t="inlineStr">
         <is>
           <t>Package</t>
         </is>
       </c>
-      <c r="I1" s="14" t="inlineStr">
+      <c r="J1" s="14" t="inlineStr">
         <is>
           <t>Voltage</t>
         </is>
       </c>
-      <c r="J1" s="14" t="inlineStr">
+      <c r="K1" s="14" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="K1" s="14" t="inlineStr">
-        <is>
-          <t>RD Decision</t>
+      <c r="L1" s="14" t="inlineStr">
+        <is>
+          <t>BOM Action</t>
         </is>
       </c>
     </row>
@@ -3669,32 +3675,29 @@
         <v>69</v>
       </c>
       <c r="E2" s="22" t="inlineStr"/>
-      <c r="F2" s="22" t="inlineStr">
+      <c r="F2" s="22" t="inlineStr"/>
+      <c r="G2" s="22" t="inlineStr"/>
+      <c r="H2" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G2" s="22" t="inlineStr">
-        <is>
-          <t>Mlcc 0.1Uf</t>
-        </is>
-      </c>
-      <c r="H2" s="22" t="inlineStr">
+      <c r="I2" s="22" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I2" s="22" t="inlineStr">
+      <c r="J2" s="22" t="inlineStr">
         <is>
           <t>16V</t>
         </is>
       </c>
-      <c r="J2" s="22" t="inlineStr">
+      <c r="K2" s="22" t="inlineStr">
         <is>
           <t>X7R</t>
         </is>
       </c>
-      <c r="K2" s="22" t="inlineStr"/>
+      <c r="L2" s="22" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="23" t="inlineStr">
@@ -3720,30 +3723,35 @@
       </c>
       <c r="F3" s="23" t="inlineStr">
         <is>
+          <t>C2501</t>
+        </is>
+      </c>
+      <c r="G3" s="23" t="inlineStr">
+        <is>
+          <t>Update 1 RefDes</t>
+        </is>
+      </c>
+      <c r="H3" s="23" t="inlineStr">
+        <is>
           <t>Same Spec</t>
         </is>
       </c>
-      <c r="G3" s="23" t="inlineStr">
-        <is>
-          <t>Mlcc 0.1Uf</t>
-        </is>
-      </c>
-      <c r="H3" s="23" t="inlineStr">
+      <c r="I3" s="23" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I3" s="23" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t>16V</t>
         </is>
       </c>
-      <c r="J3" s="23" t="inlineStr">
+      <c r="K3" s="23" t="inlineStr">
         <is>
           <t>X7R</t>
         </is>
       </c>
-      <c r="K3" s="23" t="inlineStr"/>
+      <c r="L3" s="23" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
@@ -3761,32 +3769,29 @@
         <v>4</v>
       </c>
       <c r="E4" s="22" t="inlineStr"/>
-      <c r="F4" s="22" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr"/>
+      <c r="G4" s="22" t="inlineStr"/>
+      <c r="H4" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G4" s="22" t="inlineStr">
-        <is>
-          <t>Mlcc 100Pf</t>
-        </is>
-      </c>
-      <c r="H4" s="22" t="inlineStr">
+      <c r="I4" s="22" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="J4" s="22" t="inlineStr">
         <is>
           <t>50V</t>
         </is>
       </c>
-      <c r="J4" s="22" t="inlineStr">
+      <c r="K4" s="22" t="inlineStr">
         <is>
           <t>NP0</t>
         </is>
       </c>
-      <c r="K4" s="22" t="inlineStr"/>
+      <c r="L4" s="22" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="23" t="inlineStr">
@@ -3812,30 +3817,35 @@
       </c>
       <c r="F5" s="23" t="inlineStr">
         <is>
+          <t>PC2001</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>Update 1 RefDes</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
           <t>Same Spec</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
-        <is>
-          <t>Mlcc 100Pf</t>
-        </is>
-      </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I5" s="23" t="inlineStr">
+      <c r="J5" s="23" t="inlineStr">
         <is>
           <t>50V</t>
         </is>
       </c>
-      <c r="J5" s="23" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>NP0</t>
         </is>
       </c>
-      <c r="K5" s="23" t="inlineStr"/>
+      <c r="L5" s="23" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="21" t="inlineStr">
@@ -3853,32 +3863,29 @@
         <v>2</v>
       </c>
       <c r="E6" s="22" t="inlineStr"/>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr"/>
+      <c r="G6" s="22" t="inlineStr"/>
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
-        <is>
-          <t>Mlcc 0.22Uf</t>
-        </is>
-      </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>25V</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t>X7R</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr"/>
+      <c r="L6" s="22" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="23" t="inlineStr">
@@ -3904,31 +3911,36 @@
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
+          <t>C6703</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>Update 1 RefDes</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
           <t>Vendor
 Yageo → Mlcc 0.22Uf</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
-        <is>
-          <t>Yageo → Mlcc 0.22Uf</t>
-        </is>
-      </c>
-      <c r="H7" s="23" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t>25V</t>
         </is>
       </c>
-      <c r="J7" s="23" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>X7R</t>
         </is>
       </c>
-      <c r="K7" s="23" t="inlineStr"/>
+      <c r="L7" s="23" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
@@ -3946,32 +3958,29 @@
         <v>8</v>
       </c>
       <c r="E8" s="22" t="inlineStr"/>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr"/>
+      <c r="G8" s="22" t="inlineStr"/>
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
-        <is>
-          <t>Mlcc 0.1Uf</t>
-        </is>
-      </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>0201</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>16V</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K8" s="22" t="inlineStr"/>
+      <c r="L8" s="22" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="23" t="inlineStr">
@@ -3997,31 +4006,43 @@
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
+          <t>C3325
+C3437
+C4601
+C4602
+C4603
+C4604
+C7001
+C7002</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>Update 8 RefDes</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
           <t>Vendor
 Murata → Mlcc 0.1Uf</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
-        <is>
-          <t>Murata → Mlcc 0.1Uf</t>
-        </is>
-      </c>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>0201</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t>16V</t>
         </is>
       </c>
-      <c r="J9" s="23" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K9" s="23" t="inlineStr"/>
+      <c r="L9" s="23" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
@@ -4039,32 +4060,29 @@
         <v>34</v>
       </c>
       <c r="E10" s="22" t="inlineStr"/>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr"/>
+      <c r="G10" s="22" t="inlineStr"/>
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
-        <is>
-          <t>Mlcc 0.1Uf</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>25V</t>
         </is>
       </c>
-      <c r="J10" s="22" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr">
         <is>
           <t>X7R</t>
         </is>
       </c>
-      <c r="K10" s="22" t="inlineStr"/>
+      <c r="L10" s="22" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
@@ -4090,31 +4108,40 @@
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
+          <t>PC1239
+PC1901
+PC1902
+PC1906
+PC1907</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>Update 5 RefDes</t>
+        </is>
+      </c>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
           <t>Package
 0603 → 0402</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr">
-        <is>
-          <t>Mlcc 0.1Uf</t>
-        </is>
-      </c>
-      <c r="H11" s="23" t="inlineStr">
+      <c r="I11" s="23" t="inlineStr">
         <is>
           <t>0603 → 0402</t>
         </is>
       </c>
-      <c r="I11" s="23" t="inlineStr">
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t>25V</t>
         </is>
       </c>
-      <c r="J11" s="23" t="inlineStr">
+      <c r="K11" s="23" t="inlineStr">
         <is>
           <t>X7R</t>
         </is>
       </c>
-      <c r="K11" s="23" t="inlineStr"/>
+      <c r="L11" s="23" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
@@ -4132,32 +4159,29 @@
         <v>4</v>
       </c>
       <c r="E12" s="22" t="inlineStr"/>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr"/>
+      <c r="G12" s="22" t="inlineStr"/>
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
-        <is>
-          <t>Mlcc 0.1Uf</t>
-        </is>
-      </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>50V</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t>X7R</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr"/>
+      <c r="L12" s="22" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="23" t="inlineStr">
@@ -4183,31 +4207,37 @@
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
+          <t>PC1820
+PC2024</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>Update 2 RefDes</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
           <t>Package
 0603 → 0402</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>Mlcc 0.1Uf</t>
-        </is>
-      </c>
-      <c r="H13" s="23" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>0603 → 0402</t>
         </is>
       </c>
-      <c r="I13" s="23" t="inlineStr">
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t>50V</t>
         </is>
       </c>
-      <c r="J13" s="23" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>X7R</t>
         </is>
       </c>
-      <c r="K13" s="23" t="inlineStr"/>
+      <c r="L13" s="23" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
@@ -4225,32 +4255,29 @@
         <v>25</v>
       </c>
       <c r="E14" s="22" t="inlineStr"/>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr"/>
+      <c r="G14" s="22" t="inlineStr"/>
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
-        <is>
-          <t>Walsin</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr"/>
+      <c r="L14" s="22" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
@@ -4275,6 +4302,27 @@
         <v>12</v>
       </c>
       <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>C2402
+C2403
+C4309
+C6202
+C6204
+C6205
+C6206
+C7602
+C7609
+C7615
+C7632
+C7668</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>Update 12 RefDes</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t>Vendor
 Mlcc 0.1Uf → Walsin
@@ -4282,27 +4330,22 @@
 0201 → 0402</t>
         </is>
       </c>
-      <c r="G15" s="23" t="inlineStr">
-        <is>
-          <t>Mlcc 0.1Uf → Walsin</t>
-        </is>
-      </c>
-      <c r="H15" s="23" t="inlineStr">
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>0201 → 0402</t>
         </is>
       </c>
-      <c r="I15" s="23" t="inlineStr">
+      <c r="J15" s="23" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J15" s="23" t="inlineStr">
+      <c r="K15" s="23" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K15" s="23" t="inlineStr"/>
+      <c r="L15" s="23" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
@@ -4320,32 +4363,29 @@
         <v>37</v>
       </c>
       <c r="E16" s="22" t="inlineStr"/>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr"/>
+      <c r="G16" s="22" t="inlineStr"/>
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
-        <is>
-          <t>Mlcc 10Uf</t>
-        </is>
-      </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K16" s="22" t="inlineStr"/>
+      <c r="L16" s="22" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="23" t="inlineStr">
@@ -4371,31 +4411,44 @@
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
+          <t>C5601
+C5605
+C5606
+C5633
+C5634
+C6701
+C7004
+C7010
+C7320</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>Update 9 RefDes</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
           <t>Package
 0402 → 0603</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
-        <is>
-          <t>Mlcc 10Uf</t>
-        </is>
-      </c>
-      <c r="H17" s="23" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>0402 → 0603</t>
         </is>
       </c>
-      <c r="I17" s="23" t="inlineStr">
+      <c r="J17" s="23" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J17" s="23" t="inlineStr">
+      <c r="K17" s="23" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K17" s="23" t="inlineStr"/>
+      <c r="L17" s="23" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="21" t="inlineStr">
@@ -4413,32 +4466,29 @@
         <v>12</v>
       </c>
       <c r="E18" s="22" t="inlineStr"/>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr"/>
+      <c r="G18" s="22" t="inlineStr"/>
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J18" s="22" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr">
         <is>
           <t>X6S</t>
         </is>
       </c>
-      <c r="K18" s="22" t="inlineStr"/>
+      <c r="L18" s="22" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
@@ -4463,6 +4513,22 @@
         <v>7</v>
       </c>
       <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>C3012
+C3023
+C3031
+C3032
+C3033
+C3034
+C3035</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>Update 7 RefDes</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
         <is>
           <t>Vendor
 Murata → Samsung
@@ -4470,27 +4536,22 @@
 0402 → 0603</t>
         </is>
       </c>
-      <c r="G19" s="23" t="inlineStr">
-        <is>
-          <t>Murata → Samsung</t>
-        </is>
-      </c>
-      <c r="H19" s="23" t="inlineStr">
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>0402 → 0603</t>
         </is>
       </c>
-      <c r="I19" s="23" t="inlineStr">
+      <c r="J19" s="23" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J19" s="23" t="inlineStr">
+      <c r="K19" s="23" t="inlineStr">
         <is>
           <t>X6S</t>
         </is>
       </c>
-      <c r="K19" s="23" t="inlineStr"/>
+      <c r="L19" s="23" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="21" t="inlineStr">
@@ -4508,32 +4569,29 @@
         <v>5</v>
       </c>
       <c r="E20" s="22" t="inlineStr"/>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr"/>
+      <c r="G20" s="22" t="inlineStr"/>
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
-        <is>
-          <t>Mlcc 2.2Uf</t>
-        </is>
-      </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>16V</t>
         </is>
       </c>
-      <c r="J20" s="22" t="inlineStr">
+      <c r="K20" s="22" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K20" s="22" t="inlineStr"/>
+      <c r="L20" s="22" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="23" t="inlineStr">
@@ -4558,6 +4616,20 @@
         <v>5</v>
       </c>
       <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>C8112
+C8126
+PC1510
+PC1511
+PC1516</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>Update 5 RefDes</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
         <is>
           <t>Vendor
 Murata → Mlcc 2.2Uf
@@ -4565,27 +4637,22 @@
 0402 → 0603</t>
         </is>
       </c>
-      <c r="G21" s="23" t="inlineStr">
-        <is>
-          <t>Murata → Mlcc 2.2Uf</t>
-        </is>
-      </c>
-      <c r="H21" s="23" t="inlineStr">
+      <c r="I21" s="23" t="inlineStr">
         <is>
           <t>0402 → 0603</t>
         </is>
       </c>
-      <c r="I21" s="23" t="inlineStr">
+      <c r="J21" s="23" t="inlineStr">
         <is>
           <t>16V</t>
         </is>
       </c>
-      <c r="J21" s="23" t="inlineStr">
+      <c r="K21" s="23" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K21" s="23" t="inlineStr"/>
+      <c r="L21" s="23" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
@@ -4603,32 +4670,29 @@
         <v>7</v>
       </c>
       <c r="E22" s="22" t="inlineStr"/>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr"/>
+      <c r="G22" s="22" t="inlineStr"/>
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J22" s="22" t="inlineStr">
+      <c r="K22" s="22" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K22" s="22" t="inlineStr"/>
+      <c r="L22" s="22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="23" t="inlineStr">
@@ -4653,6 +4717,17 @@
         <v>2</v>
       </c>
       <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>C3326
+C3438</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>Update 2 RefDes</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
         <is>
           <t>Vendor
 Mlcc 2.2Uf → Murata
@@ -4660,27 +4735,22 @@
 0201 → 0402</t>
         </is>
       </c>
-      <c r="G23" s="23" t="inlineStr">
-        <is>
-          <t>Mlcc 2.2Uf → Murata</t>
-        </is>
-      </c>
-      <c r="H23" s="23" t="inlineStr">
+      <c r="I23" s="23" t="inlineStr">
         <is>
           <t>0201 → 0402</t>
         </is>
       </c>
-      <c r="I23" s="23" t="inlineStr">
+      <c r="J23" s="23" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J23" s="23" t="inlineStr">
+      <c r="K23" s="23" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K23" s="23" t="inlineStr"/>
+      <c r="L23" s="23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="21" t="inlineStr">
@@ -4698,32 +4768,29 @@
         <v>4</v>
       </c>
       <c r="E24" s="22" t="inlineStr"/>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr"/>
+      <c r="G24" s="22" t="inlineStr"/>
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
-        <is>
-          <t>Mlcc 0.33Uf</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>0201</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="J24" s="22" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J24" s="22" t="inlineStr">
+      <c r="K24" s="22" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K24" s="22" t="inlineStr"/>
+      <c r="L24" s="22" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="23" t="inlineStr">
@@ -4749,31 +4816,37 @@
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
+          <t>C7314
+C7315</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>Update 2 RefDes</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
           <t>Package
 0402 → 0201</t>
         </is>
       </c>
-      <c r="G25" s="23" t="inlineStr">
-        <is>
-          <t>Mlcc 0.33Uf</t>
-        </is>
-      </c>
-      <c r="H25" s="23" t="inlineStr">
+      <c r="I25" s="23" t="inlineStr">
         <is>
           <t>0402 → 0201</t>
         </is>
       </c>
-      <c r="I25" s="23" t="inlineStr">
+      <c r="J25" s="23" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J25" s="23" t="inlineStr">
+      <c r="K25" s="23" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K25" s="23" t="inlineStr"/>
+      <c r="L25" s="23" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
@@ -4791,32 +4864,29 @@
         <v>4</v>
       </c>
       <c r="E26" s="22" t="inlineStr"/>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr"/>
+      <c r="G26" s="22" t="inlineStr"/>
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
-        <is>
-          <t>Mlcc 0.01Uf</t>
-        </is>
-      </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="J26" s="22" t="inlineStr">
         <is>
           <t>25V</t>
         </is>
       </c>
-      <c r="J26" s="22" t="inlineStr">
+      <c r="K26" s="22" t="inlineStr">
         <is>
           <t>X7R</t>
         </is>
       </c>
-      <c r="K26" s="22" t="inlineStr"/>
+      <c r="L26" s="22" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
@@ -4842,31 +4912,37 @@
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
+          <t>C7201
+C7203</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>Update 2 RefDes</t>
+        </is>
+      </c>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
           <t>Voltage
 50V → 25V</t>
         </is>
       </c>
-      <c r="G27" s="23" t="inlineStr">
-        <is>
-          <t>Mlcc 0.01Uf</t>
-        </is>
-      </c>
-      <c r="H27" s="23" t="inlineStr">
+      <c r="I27" s="23" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I27" s="23" t="inlineStr">
+      <c r="J27" s="23" t="inlineStr">
         <is>
           <t>50V → 25V</t>
         </is>
       </c>
-      <c r="J27" s="23" t="inlineStr">
+      <c r="K27" s="23" t="inlineStr">
         <is>
           <t>X7R</t>
         </is>
       </c>
-      <c r="K27" s="23" t="inlineStr"/>
+      <c r="L27" s="23" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="21" t="inlineStr">
@@ -4884,32 +4960,29 @@
         <v>11</v>
       </c>
       <c r="E28" s="22" t="inlineStr"/>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr"/>
+      <c r="G28" s="22" t="inlineStr"/>
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
-        <is>
-          <t>Mlcc 1Uf</t>
-        </is>
-      </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I28" s="22" t="inlineStr">
+      <c r="J28" s="22" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J28" s="22" t="inlineStr">
+      <c r="K28" s="22" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K28" s="22" t="inlineStr"/>
+      <c r="L28" s="22" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="23" t="inlineStr">
@@ -4934,6 +5007,19 @@
         <v>4</v>
       </c>
       <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>C7614
+C7626
+C7639
+C7640</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>Update 4 RefDes</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
         <is>
           <t>Vendor
 Murata → Mlcc 1Uf
@@ -4941,27 +5027,22 @@
 50V → 6.3V</t>
         </is>
       </c>
-      <c r="G29" s="23" t="inlineStr">
-        <is>
-          <t>Murata → Mlcc 1Uf</t>
-        </is>
-      </c>
-      <c r="H29" s="23" t="inlineStr">
+      <c r="I29" s="23" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I29" s="23" t="inlineStr">
+      <c r="J29" s="23" t="inlineStr">
         <is>
           <t>50V → 6.3V</t>
         </is>
       </c>
-      <c r="J29" s="23" t="inlineStr">
+      <c r="K29" s="23" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K29" s="23" t="inlineStr"/>
+      <c r="L29" s="23" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="23" t="inlineStr">
@@ -4987,31 +5068,37 @@
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
+          <t>C4327
+C8140</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>Update 2 RefDes</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
           <t>Voltage
 16V → 6.3V</t>
         </is>
       </c>
-      <c r="G30" s="23" t="inlineStr">
-        <is>
-          <t>Mlcc 1Uf</t>
-        </is>
-      </c>
-      <c r="H30" s="23" t="inlineStr">
+      <c r="I30" s="23" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I30" s="23" t="inlineStr">
+      <c r="J30" s="23" t="inlineStr">
         <is>
           <t>16V → 6.3V</t>
         </is>
       </c>
-      <c r="J30" s="23" t="inlineStr">
+      <c r="K30" s="23" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K30" s="23" t="inlineStr"/>
+      <c r="L30" s="23" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="21" t="inlineStr">
@@ -5029,32 +5116,29 @@
         <v>3</v>
       </c>
       <c r="E31" s="22" t="inlineStr"/>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr"/>
+      <c r="G31" s="22" t="inlineStr"/>
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
-        <is>
-          <t>Mlcc 1Uf</t>
-        </is>
-      </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="I31" s="22" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="I31" s="22" t="inlineStr">
+      <c r="J31" s="22" t="inlineStr">
         <is>
           <t>10V</t>
         </is>
       </c>
-      <c r="J31" s="22" t="inlineStr">
+      <c r="K31" s="22" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K31" s="22" t="inlineStr"/>
+      <c r="L31" s="22" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
@@ -5079,6 +5163,17 @@
         <v>2</v>
       </c>
       <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>PC1249
+PC1824</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>Update 2 RefDes</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
         <is>
           <t>Vendor
 Murata → Mlcc 1Uf
@@ -5086,27 +5181,22 @@
 25V → 10V</t>
         </is>
       </c>
-      <c r="G32" s="23" t="inlineStr">
-        <is>
-          <t>Murata → Mlcc 1Uf</t>
-        </is>
-      </c>
-      <c r="H32" s="23" t="inlineStr">
+      <c r="I32" s="23" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="I32" s="23" t="inlineStr">
+      <c r="J32" s="23" t="inlineStr">
         <is>
           <t>25V → 10V</t>
         </is>
       </c>
-      <c r="J32" s="23" t="inlineStr">
+      <c r="K32" s="23" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K32" s="23" t="inlineStr"/>
+      <c r="L32" s="23" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="21" t="inlineStr">
@@ -5124,32 +5214,29 @@
         <v>6</v>
       </c>
       <c r="E33" s="22" t="inlineStr"/>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr"/>
+      <c r="G33" s="22" t="inlineStr"/>
+      <c r="H33" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
-        <is>
-          <t>Mlcc 0.22Uf</t>
-        </is>
-      </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="I33" s="22" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="J33" s="22" t="inlineStr">
         <is>
           <t>10V</t>
         </is>
       </c>
-      <c r="J33" s="22" t="inlineStr">
+      <c r="K33" s="22" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K33" s="22" t="inlineStr"/>
+      <c r="L33" s="22" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="23" t="inlineStr">
@@ -5174,6 +5261,17 @@
         <v>2</v>
       </c>
       <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>C8155
+PC1205</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>Update 2 RefDes</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
         <is>
           <t>Vendor
 Samsung → Mlcc 0.22Uf
@@ -5181,27 +5279,22 @@
 6.3V → 10V</t>
         </is>
       </c>
-      <c r="G34" s="23" t="inlineStr">
-        <is>
-          <t>Samsung → Mlcc 0.22Uf</t>
-        </is>
-      </c>
-      <c r="H34" s="23" t="inlineStr">
+      <c r="I34" s="23" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I34" s="23" t="inlineStr">
+      <c r="J34" s="23" t="inlineStr">
         <is>
           <t>6.3V → 10V</t>
         </is>
       </c>
-      <c r="J34" s="23" t="inlineStr">
+      <c r="K34" s="23" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K34" s="23" t="inlineStr"/>
+      <c r="L34" s="23" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="21" t="inlineStr">
@@ -5219,32 +5312,29 @@
         <v>2</v>
       </c>
       <c r="E35" s="22" t="inlineStr"/>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr"/>
+      <c r="G35" s="22" t="inlineStr"/>
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G35" s="22" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="I35" s="22" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I35" s="22" t="inlineStr">
+      <c r="J35" s="22" t="inlineStr">
         <is>
           <t>50V</t>
         </is>
       </c>
-      <c r="J35" s="22" t="inlineStr">
+      <c r="K35" s="22" t="inlineStr">
         <is>
           <t>X7R</t>
         </is>
       </c>
-      <c r="K35" s="22" t="inlineStr"/>
+      <c r="L35" s="22" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="23" t="inlineStr">
@@ -5270,31 +5360,36 @@
       </c>
       <c r="F36" s="23" t="inlineStr">
         <is>
+          <t>C5707</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>Update 1 RefDes</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
           <t>Voltage
 16V → 50V</t>
         </is>
       </c>
-      <c r="G36" s="23" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="H36" s="23" t="inlineStr">
+      <c r="I36" s="23" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I36" s="23" t="inlineStr">
+      <c r="J36" s="23" t="inlineStr">
         <is>
           <t>16V → 50V</t>
         </is>
       </c>
-      <c r="J36" s="23" t="inlineStr">
+      <c r="K36" s="23" t="inlineStr">
         <is>
           <t>X7R</t>
         </is>
       </c>
-      <c r="K36" s="23" t="inlineStr"/>
+      <c r="L36" s="23" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="21" t="inlineStr">
@@ -5312,32 +5407,29 @@
         <v>11</v>
       </c>
       <c r="E37" s="22" t="inlineStr"/>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr"/>
+      <c r="G37" s="22" t="inlineStr"/>
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G37" s="22" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="I37" s="22" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="I37" s="22" t="inlineStr">
+      <c r="J37" s="22" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J37" s="22" t="inlineStr">
+      <c r="K37" s="22" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K37" s="22" t="inlineStr"/>
+      <c r="L37" s="22" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="23" t="inlineStr">
@@ -5363,31 +5455,36 @@
       </c>
       <c r="F38" s="23" t="inlineStr">
         <is>
+          <t>PC0601</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>Update 1 RefDes</t>
+        </is>
+      </c>
+      <c r="H38" s="23" t="inlineStr">
+        <is>
           <t>Voltage
 25V → 6.3V</t>
         </is>
       </c>
-      <c r="G38" s="23" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="H38" s="23" t="inlineStr">
+      <c r="I38" s="23" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="I38" s="23" t="inlineStr">
+      <c r="J38" s="23" t="inlineStr">
         <is>
           <t>25V → 6.3V</t>
         </is>
       </c>
-      <c r="J38" s="23" t="inlineStr">
+      <c r="K38" s="23" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K38" s="23" t="inlineStr"/>
+      <c r="L38" s="23" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="21" t="inlineStr">
@@ -5405,32 +5502,29 @@
         <v>1</v>
       </c>
       <c r="E39" s="22" t="inlineStr"/>
-      <c r="F39" s="22" t="inlineStr">
+      <c r="F39" s="22" t="inlineStr"/>
+      <c r="G39" s="22" t="inlineStr"/>
+      <c r="H39" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G39" s="22" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="H39" s="22" t="inlineStr">
+      <c r="I39" s="22" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I39" s="22" t="inlineStr">
+      <c r="J39" s="22" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J39" s="22" t="inlineStr">
+      <c r="K39" s="22" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K39" s="22" t="inlineStr"/>
+      <c r="L39" s="22" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="23" t="inlineStr">
@@ -5456,31 +5550,36 @@
       </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
+          <t>C8128</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>Update 1 RefDes</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
           <t>Voltage
 16V → 6.3V</t>
         </is>
       </c>
-      <c r="G40" s="23" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="H40" s="23" t="inlineStr">
+      <c r="I40" s="23" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I40" s="23" t="inlineStr">
+      <c r="J40" s="23" t="inlineStr">
         <is>
           <t>16V → 6.3V</t>
         </is>
       </c>
-      <c r="J40" s="23" t="inlineStr">
+      <c r="K40" s="23" t="inlineStr">
         <is>
           <t>X5R</t>
         </is>
       </c>
-      <c r="K40" s="23" t="inlineStr"/>
+      <c r="L40" s="23" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
@@ -5498,32 +5597,29 @@
         <v>1</v>
       </c>
       <c r="E41" s="22" t="inlineStr"/>
-      <c r="F41" s="22" t="inlineStr">
+      <c r="F41" s="22" t="inlineStr"/>
+      <c r="G41" s="22" t="inlineStr"/>
+      <c r="H41" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G41" s="22" t="inlineStr">
-        <is>
-          <t>Mlcc 2200Pf</t>
-        </is>
-      </c>
-      <c r="H41" s="22" t="inlineStr">
+      <c r="I41" s="22" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I41" s="22" t="inlineStr">
+      <c r="J41" s="22" t="inlineStr">
         <is>
           <t>50V</t>
         </is>
       </c>
-      <c r="J41" s="22" t="inlineStr">
+      <c r="K41" s="22" t="inlineStr">
         <is>
           <t>X7R</t>
         </is>
       </c>
-      <c r="K41" s="22" t="inlineStr"/>
+      <c r="L41" s="22" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="23" t="inlineStr">
@@ -5548,6 +5644,16 @@
         <v>1</v>
       </c>
       <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>C8116</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>Update 1 RefDes</t>
+        </is>
+      </c>
+      <c r="H42" s="23" t="inlineStr">
         <is>
           <t>Vendor
 Murata → Mlcc 2200Pf
@@ -5555,27 +5661,22 @@
 X5R → X7R</t>
         </is>
       </c>
-      <c r="G42" s="23" t="inlineStr">
-        <is>
-          <t>Murata → Mlcc 2200Pf</t>
-        </is>
-      </c>
-      <c r="H42" s="23" t="inlineStr">
+      <c r="I42" s="23" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I42" s="23" t="inlineStr">
+      <c r="J42" s="23" t="inlineStr">
         <is>
           <t>50V</t>
         </is>
       </c>
-      <c r="J42" s="23" t="inlineStr">
+      <c r="K42" s="23" t="inlineStr">
         <is>
           <t>X5R → X7R</t>
         </is>
       </c>
-      <c r="K42" s="23" t="inlineStr"/>
+      <c r="L42" s="23" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="21" t="inlineStr">
@@ -5593,32 +5694,29 @@
         <v>55</v>
       </c>
       <c r="E43" s="22" t="inlineStr"/>
-      <c r="F43" s="22" t="inlineStr">
+      <c r="F43" s="22" t="inlineStr"/>
+      <c r="G43" s="22" t="inlineStr"/>
+      <c r="H43" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G43" s="22" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="H43" s="22" t="inlineStr">
+      <c r="I43" s="22" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="I43" s="22" t="inlineStr">
+      <c r="J43" s="22" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J43" s="22" t="inlineStr">
+      <c r="K43" s="22" t="inlineStr">
         <is>
           <t>X6S</t>
         </is>
       </c>
-      <c r="K43" s="22" t="inlineStr"/>
+      <c r="L43" s="22" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="23" t="inlineStr">
@@ -5644,31 +5742,80 @@
       </c>
       <c r="F44" s="23" t="inlineStr">
         <is>
+          <t>C6712
+C6811
+C6812
+C6911
+C6912
+C7121
+C7129
+C7311
+C7324
+C7604
+C7617
+C7619
+C7620
+C7621
+PC1102
+PC1106
+PC1107
+PC1125
+PC1126
+PC1209
+PC1210
+PC1238
+PC1244
+PC1245
+PC1251
+PC1252
+PC1306
+PC1307
+PC1308
+PC1310
+PC1311
+PC1312
+PC1313
+PC1904
+PC1905
+PC1909
+PC1910
+PO1101
+PO1102
+PO1103
+PO1104
+PO1201
+PO1302
+PO1901
+PO1902</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr">
+        <is>
+          <t>Update 45 RefDes</t>
+        </is>
+      </c>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
           <t>Material
 X5R → X6S</t>
         </is>
       </c>
-      <c r="G44" s="23" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="H44" s="23" t="inlineStr">
+      <c r="I44" s="23" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="I44" s="23" t="inlineStr">
+      <c r="J44" s="23" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J44" s="23" t="inlineStr">
+      <c r="K44" s="23" t="inlineStr">
         <is>
           <t>X5R → X6S</t>
         </is>
       </c>
-      <c r="K44" s="23" t="inlineStr"/>
+      <c r="L44" s="23" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="21" t="inlineStr">
@@ -5686,32 +5833,29 @@
         <v>8</v>
       </c>
       <c r="E45" s="22" t="inlineStr"/>
-      <c r="F45" s="22" t="inlineStr">
+      <c r="F45" s="22" t="inlineStr"/>
+      <c r="G45" s="22" t="inlineStr"/>
+      <c r="H45" s="22" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G45" s="22" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="H45" s="22" t="inlineStr">
+      <c r="I45" s="22" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I45" s="22" t="inlineStr">
+      <c r="J45" s="22" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J45" s="22" t="inlineStr">
+      <c r="K45" s="22" t="inlineStr">
         <is>
           <t>X6S</t>
         </is>
       </c>
-      <c r="K45" s="22" t="inlineStr"/>
+      <c r="L45" s="22" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="23" t="inlineStr">
@@ -5736,6 +5880,23 @@
         <v>8</v>
       </c>
       <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>C5631
+C6708
+C6711
+C6715
+C7603
+C7616
+C7631
+C8114</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr">
+        <is>
+          <t>Update 8 RefDes</t>
+        </is>
+      </c>
+      <c r="H46" s="23" t="inlineStr">
         <is>
           <t>Vendor
 Samsung → Murata
@@ -5743,27 +5904,22 @@
 X5R → X6S</t>
         </is>
       </c>
-      <c r="G46" s="23" t="inlineStr">
-        <is>
-          <t>Samsung → Murata</t>
-        </is>
-      </c>
-      <c r="H46" s="23" t="inlineStr">
+      <c r="I46" s="23" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="I46" s="23" t="inlineStr">
+      <c r="J46" s="23" t="inlineStr">
         <is>
           <t>6.3V</t>
         </is>
       </c>
-      <c r="J46" s="23" t="inlineStr">
+      <c r="K46" s="23" t="inlineStr">
         <is>
           <t>X5R → X6S</t>
         </is>
       </c>
-      <c r="K46" s="23" t="inlineStr"/>
+      <c r="L46" s="23" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="21" t="inlineStr"/>
@@ -5777,6 +5933,7 @@
       <c r="I47" s="22" t="inlineStr"/>
       <c r="J47" s="22" t="inlineStr"/>
       <c r="K47" s="22" t="inlineStr"/>
+      <c r="L47" s="22" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="21" t="inlineStr"/>
@@ -5790,6 +5947,7 @@
       <c r="I48" s="22" t="inlineStr"/>
       <c r="J48" s="22" t="inlineStr"/>
       <c r="K48" s="22" t="inlineStr"/>
+      <c r="L48" s="22" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="21" t="inlineStr"/>
@@ -5803,6 +5961,7 @@
       <c r="I49" s="22" t="inlineStr"/>
       <c r="J49" s="22" t="inlineStr"/>
       <c r="K49" s="22" t="inlineStr"/>
+      <c r="L49" s="22" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr"/>
@@ -5816,6 +5975,7 @@
       <c r="I50" s="22" t="inlineStr"/>
       <c r="J50" s="22" t="inlineStr"/>
       <c r="K50" s="22" t="inlineStr"/>
+      <c r="L50" s="22" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="21" t="inlineStr"/>
@@ -5829,6 +5989,7 @@
       <c r="I51" s="22" t="inlineStr"/>
       <c r="J51" s="22" t="inlineStr"/>
       <c r="K51" s="22" t="inlineStr"/>
+      <c r="L51" s="22" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="21" t="inlineStr"/>
@@ -5842,6 +6003,7 @@
       <c r="I52" s="22" t="inlineStr"/>
       <c r="J52" s="22" t="inlineStr"/>
       <c r="K52" s="22" t="inlineStr"/>
+      <c r="L52" s="22" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="21" t="inlineStr"/>
@@ -5855,6 +6017,7 @@
       <c r="I53" s="22" t="inlineStr"/>
       <c r="J53" s="22" t="inlineStr"/>
       <c r="K53" s="22" t="inlineStr"/>
+      <c r="L53" s="22" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="21" t="inlineStr"/>
@@ -5868,6 +6031,7 @@
       <c r="I54" s="22" t="inlineStr"/>
       <c r="J54" s="22" t="inlineStr"/>
       <c r="K54" s="22" t="inlineStr"/>
+      <c r="L54" s="22" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="21" t="inlineStr"/>
@@ -5881,6 +6045,7 @@
       <c r="I55" s="22" t="inlineStr"/>
       <c r="J55" s="22" t="inlineStr"/>
       <c r="K55" s="22" t="inlineStr"/>
+      <c r="L55" s="22" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="21" t="inlineStr"/>
@@ -5894,6 +6059,7 @@
       <c r="I56" s="22" t="inlineStr"/>
       <c r="J56" s="22" t="inlineStr"/>
       <c r="K56" s="22" t="inlineStr"/>
+      <c r="L56" s="22" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="21" t="inlineStr"/>
@@ -5907,6 +6073,7 @@
       <c r="I57" s="22" t="inlineStr"/>
       <c r="J57" s="22" t="inlineStr"/>
       <c r="K57" s="22" t="inlineStr"/>
+      <c r="L57" s="22" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="21" t="inlineStr"/>
@@ -5920,6 +6087,7 @@
       <c r="I58" s="22" t="inlineStr"/>
       <c r="J58" s="22" t="inlineStr"/>
       <c r="K58" s="22" t="inlineStr"/>
+      <c r="L58" s="22" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="21" t="inlineStr"/>
@@ -5933,6 +6101,7 @@
       <c r="I59" s="22" t="inlineStr"/>
       <c r="J59" s="22" t="inlineStr"/>
       <c r="K59" s="22" t="inlineStr"/>
+      <c r="L59" s="22" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="21" t="inlineStr"/>
@@ -5946,6 +6115,7 @@
       <c r="I60" s="22" t="inlineStr"/>
       <c r="J60" s="22" t="inlineStr"/>
       <c r="K60" s="22" t="inlineStr"/>
+      <c r="L60" s="22" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="21" t="inlineStr"/>
@@ -5959,6 +6129,7 @@
       <c r="I61" s="22" t="inlineStr"/>
       <c r="J61" s="22" t="inlineStr"/>
       <c r="K61" s="22" t="inlineStr"/>
+      <c r="L61" s="22" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="21" t="inlineStr"/>
@@ -5972,6 +6143,7 @@
       <c r="I62" s="22" t="inlineStr"/>
       <c r="J62" s="22" t="inlineStr"/>
       <c r="K62" s="22" t="inlineStr"/>
+      <c r="L62" s="22" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="21" t="inlineStr"/>
@@ -5985,6 +6157,7 @@
       <c r="I63" s="22" t="inlineStr"/>
       <c r="J63" s="22" t="inlineStr"/>
       <c r="K63" s="22" t="inlineStr"/>
+      <c r="L63" s="22" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="21" t="inlineStr"/>
@@ -5998,6 +6171,7 @@
       <c r="I64" s="22" t="inlineStr"/>
       <c r="J64" s="22" t="inlineStr"/>
       <c r="K64" s="22" t="inlineStr"/>
+      <c r="L64" s="22" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="21" t="inlineStr"/>
@@ -6011,6 +6185,7 @@
       <c r="I65" s="22" t="inlineStr"/>
       <c r="J65" s="22" t="inlineStr"/>
       <c r="K65" s="22" t="inlineStr"/>
+      <c r="L65" s="22" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="21" t="inlineStr"/>
@@ -6024,6 +6199,7 @@
       <c r="I66" s="22" t="inlineStr"/>
       <c r="J66" s="22" t="inlineStr"/>
       <c r="K66" s="22" t="inlineStr"/>
+      <c r="L66" s="22" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="21" t="inlineStr"/>
@@ -6037,6 +6213,7 @@
       <c r="I67" s="22" t="inlineStr"/>
       <c r="J67" s="22" t="inlineStr"/>
       <c r="K67" s="22" t="inlineStr"/>
+      <c r="L67" s="22" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="21" t="inlineStr"/>
@@ -6050,12 +6227,13 @@
       <c r="I68" s="22" t="inlineStr"/>
       <c r="J68" s="22" t="inlineStr"/>
       <c r="K68" s="22" t="inlineStr"/>
+      <c r="L68" s="22" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K68"/>
+  <autoFilter ref="A1:L68"/>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid RD Decision" error="Please choose Merge, Keep, or Skip." promptTitle="RD Decision" prompt="Select the engineering decision for this merge row." type="list">
-      <formula1>"Merge,Keep,Skip"</formula1>
+    <dataValidation sqref="L2:L1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid BOM Action" error="Please choose Update BOM, No Change, or Investigate." promptTitle="BOM Action" prompt="Select the BOM action for this merge row." type="list">
+      <formula1>"Update BOM,No Change,Investigate"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6068,7 +6246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6079,7 +6257,6 @@
     <col width="32" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col hidden="1" width="11" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -6123,11 +6300,6 @@
           <t>Group</t>
         </is>
       </c>
-      <c r="I1" s="14" t="inlineStr">
-        <is>
-          <t>RD Decision</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
@@ -6166,11 +6338,6 @@
           <t>R001</t>
         </is>
       </c>
-      <c r="I2" s="16" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
@@ -6209,11 +6376,6 @@
           <t>R002</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
@@ -6252,11 +6414,6 @@
           <t>R003</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
@@ -6295,11 +6452,6 @@
           <t>R004</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
@@ -6338,11 +6490,6 @@
           <t>R005</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
@@ -6381,11 +6528,6 @@
           <t>R006</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
@@ -6424,11 +6566,6 @@
           <t>R007</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
@@ -6467,11 +6604,6 @@
           <t>R008</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
@@ -6510,11 +6642,6 @@
           <t>R009</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
@@ -6553,11 +6680,6 @@
           <t>R010</t>
         </is>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
@@ -6596,11 +6718,6 @@
           <t>R011</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
@@ -6639,11 +6756,6 @@
           <t>R012</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
@@ -6682,11 +6794,6 @@
           <t>R013</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
@@ -6725,11 +6832,6 @@
           <t>R014</t>
         </is>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
@@ -6768,11 +6870,6 @@
           <t>R015</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="inlineStr">
@@ -6811,11 +6908,6 @@
           <t>R016</t>
         </is>
       </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
@@ -6854,11 +6946,6 @@
           <t>R017</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
@@ -6897,11 +6984,6 @@
           <t>R018</t>
         </is>
       </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
@@ -6940,11 +7022,6 @@
           <t>R019</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
@@ -6983,11 +7060,6 @@
           <t>R020</t>
         </is>
       </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
@@ -7026,11 +7098,6 @@
           <t>R021</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
@@ -7069,11 +7136,6 @@
           <t>R022</t>
         </is>
       </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
@@ -7112,11 +7174,6 @@
           <t>R023</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
@@ -7155,11 +7212,6 @@
           <t>R024</t>
         </is>
       </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
@@ -7198,11 +7250,6 @@
           <t>R025</t>
         </is>
       </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
@@ -7241,14 +7288,9 @@
           <t>R026</t>
         </is>
       </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>⏳ 待处理 (Pending)</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I27"/>
+  <autoFilter ref="A1:H27"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
